--- a/ملفات_للتحميل/test_subscriptions_EN.xlsx
+++ b/ملفات_للتحميل/test_subscriptions_EN.xlsx
@@ -397,16 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G341"/>
-  <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G491"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8251,9 +8242,3459 @@
         <v>Paid in cash at the office</v>
       </c>
     </row>
+    <row r="342">
+      <c r="A342">
+        <v>1</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Bakri</v>
+      </c>
+      <c r="D342">
+        <v>2026</v>
+      </c>
+      <c r="E342">
+        <v>150000</v>
+      </c>
+      <c r="F342" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="G342" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>2</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Hanan</v>
+      </c>
+      <c r="C343" t="str">
+        <v>Khoury</v>
+      </c>
+      <c r="D343">
+        <v>2026</v>
+      </c>
+      <c r="E343">
+        <v>150000</v>
+      </c>
+      <c r="F343" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="G343" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>3</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Jalal</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Sabbagh</v>
+      </c>
+      <c r="D344">
+        <v>2026</v>
+      </c>
+      <c r="E344">
+        <v>150000</v>
+      </c>
+      <c r="F344" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="G344" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>4</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Rami</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Othman</v>
+      </c>
+      <c r="D345">
+        <v>2026</v>
+      </c>
+      <c r="E345">
+        <v>150000</v>
+      </c>
+      <c r="F345" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="G345" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>5</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Lina</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Saadeh</v>
+      </c>
+      <c r="D346">
+        <v>2026</v>
+      </c>
+      <c r="E346">
+        <v>150000</v>
+      </c>
+      <c r="F346" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="G346" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>6</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Adnan</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Mardam-Bey</v>
+      </c>
+      <c r="D347">
+        <v>2026</v>
+      </c>
+      <c r="E347">
+        <v>150000</v>
+      </c>
+      <c r="F347" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="G347" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>7</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Naji</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D348">
+        <v>2026</v>
+      </c>
+      <c r="E348">
+        <v>150000</v>
+      </c>
+      <c r="F348" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="G348" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>8</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Tarek</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Mardam-Bey</v>
+      </c>
+      <c r="D349">
+        <v>2026</v>
+      </c>
+      <c r="E349">
+        <v>150000</v>
+      </c>
+      <c r="F349" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="G349" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>9</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Ibrahim</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Yacoub</v>
+      </c>
+      <c r="D350">
+        <v>2026</v>
+      </c>
+      <c r="E350">
+        <v>150000</v>
+      </c>
+      <c r="F350" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G350" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>10</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Majd</v>
+      </c>
+      <c r="C351" t="str">
+        <v>Sayegh</v>
+      </c>
+      <c r="D351">
+        <v>2026</v>
+      </c>
+      <c r="E351">
+        <v>150000</v>
+      </c>
+      <c r="F351" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="G351" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>11</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Bilal</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Najjar</v>
+      </c>
+      <c r="D352">
+        <v>2026</v>
+      </c>
+      <c r="E352">
+        <v>150000</v>
+      </c>
+      <c r="F352" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="G352" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>12</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Yousef</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D353">
+        <v>2026</v>
+      </c>
+      <c r="E353">
+        <v>150000</v>
+      </c>
+      <c r="F353" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="G353" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>13</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Al-Tartousi</v>
+      </c>
+      <c r="D354">
+        <v>2026</v>
+      </c>
+      <c r="E354">
+        <v>150000</v>
+      </c>
+      <c r="F354" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="G354" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>14</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Sami</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="D355">
+        <v>2026</v>
+      </c>
+      <c r="E355">
+        <v>150000</v>
+      </c>
+      <c r="F355" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="G355" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>15</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Fares</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Habib</v>
+      </c>
+      <c r="D356">
+        <v>2026</v>
+      </c>
+      <c r="E356">
+        <v>150000</v>
+      </c>
+      <c r="F356" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="G356" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>16</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Ghada</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Al-Khatib</v>
+      </c>
+      <c r="D357">
+        <v>2026</v>
+      </c>
+      <c r="E357">
+        <v>150000</v>
+      </c>
+      <c r="F357" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G357" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>17</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Sami</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Sayegh</v>
+      </c>
+      <c r="D358">
+        <v>2026</v>
+      </c>
+      <c r="E358">
+        <v>150000</v>
+      </c>
+      <c r="F358" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="G358" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>18</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Marwan</v>
+      </c>
+      <c r="C359" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="D359">
+        <v>2026</v>
+      </c>
+      <c r="E359">
+        <v>150000</v>
+      </c>
+      <c r="F359" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="G359" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>19</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Ghada</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Mansour</v>
+      </c>
+      <c r="D360">
+        <v>2026</v>
+      </c>
+      <c r="E360">
+        <v>150000</v>
+      </c>
+      <c r="F360" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="G360" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>20</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Ziad</v>
+      </c>
+      <c r="C361" t="str">
+        <v>Mansour</v>
+      </c>
+      <c r="D361">
+        <v>2026</v>
+      </c>
+      <c r="E361">
+        <v>150000</v>
+      </c>
+      <c r="F361" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="G361" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>21</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Malek</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Al-Hamwi</v>
+      </c>
+      <c r="D362">
+        <v>2026</v>
+      </c>
+      <c r="E362">
+        <v>150000</v>
+      </c>
+      <c r="F362" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="G362" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>22</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Malek</v>
+      </c>
+      <c r="C363" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D363">
+        <v>2026</v>
+      </c>
+      <c r="E363">
+        <v>150000</v>
+      </c>
+      <c r="F363" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="G363" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>23</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Wafa</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D364">
+        <v>2026</v>
+      </c>
+      <c r="E364">
+        <v>150000</v>
+      </c>
+      <c r="F364" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="G364" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>24</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Souad</v>
+      </c>
+      <c r="C365" t="str">
+        <v>Abdo</v>
+      </c>
+      <c r="D365">
+        <v>2026</v>
+      </c>
+      <c r="E365">
+        <v>150000</v>
+      </c>
+      <c r="F365" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="G365" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>25</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Salma</v>
+      </c>
+      <c r="C366" t="str">
+        <v>Al-Idlibi</v>
+      </c>
+      <c r="D366">
+        <v>2026</v>
+      </c>
+      <c r="E366">
+        <v>150000</v>
+      </c>
+      <c r="F366" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="G366" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>26</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Sami</v>
+      </c>
+      <c r="C367" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D367">
+        <v>2026</v>
+      </c>
+      <c r="E367">
+        <v>150000</v>
+      </c>
+      <c r="F367" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="G367" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>27</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Nour</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Mardini</v>
+      </c>
+      <c r="D368">
+        <v>2026</v>
+      </c>
+      <c r="E368">
+        <v>150000</v>
+      </c>
+      <c r="F368" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="G368" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>28</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Naji</v>
+      </c>
+      <c r="C369" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D369">
+        <v>2026</v>
+      </c>
+      <c r="E369">
+        <v>150000</v>
+      </c>
+      <c r="F369" t="str">
+        <v>2026-01-11</v>
+      </c>
+      <c r="G369" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>29</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Tamer</v>
+      </c>
+      <c r="C370" t="str">
+        <v>Mardini</v>
+      </c>
+      <c r="D370">
+        <v>2026</v>
+      </c>
+      <c r="E370">
+        <v>150000</v>
+      </c>
+      <c r="F370" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="G370" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>30</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Sara</v>
+      </c>
+      <c r="C371" t="str">
+        <v>Younis</v>
+      </c>
+      <c r="D371">
+        <v>2026</v>
+      </c>
+      <c r="E371">
+        <v>150000</v>
+      </c>
+      <c r="F371" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="G371" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>31</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Usama</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D372">
+        <v>2026</v>
+      </c>
+      <c r="E372">
+        <v>150000</v>
+      </c>
+      <c r="F372" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="G372" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>32</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Saif</v>
+      </c>
+      <c r="C373" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D373">
+        <v>2026</v>
+      </c>
+      <c r="E373">
+        <v>150000</v>
+      </c>
+      <c r="F373" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="G373" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>33</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Majd</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D374">
+        <v>2026</v>
+      </c>
+      <c r="E374">
+        <v>150000</v>
+      </c>
+      <c r="F374" t="str">
+        <v>2026-01-18</v>
+      </c>
+      <c r="G374" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>34</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Fadi</v>
+      </c>
+      <c r="C375" t="str">
+        <v>Bakri</v>
+      </c>
+      <c r="D375">
+        <v>2026</v>
+      </c>
+      <c r="E375">
+        <v>150000</v>
+      </c>
+      <c r="F375" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="G375" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>35</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Ruba</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D376">
+        <v>2026</v>
+      </c>
+      <c r="E376">
+        <v>150000</v>
+      </c>
+      <c r="F376" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="G376" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>36</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Bushra</v>
+      </c>
+      <c r="C377" t="str">
+        <v>Hafez</v>
+      </c>
+      <c r="D377">
+        <v>2026</v>
+      </c>
+      <c r="E377">
+        <v>150000</v>
+      </c>
+      <c r="F377" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="G377" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>37</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Houda</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D378">
+        <v>2026</v>
+      </c>
+      <c r="E378">
+        <v>150000</v>
+      </c>
+      <c r="F378" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="G378" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>38</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Omar</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Al-Dimashqi</v>
+      </c>
+      <c r="D379">
+        <v>2026</v>
+      </c>
+      <c r="E379">
+        <v>150000</v>
+      </c>
+      <c r="F379" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="G379" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>39</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Tarek</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Al-Kuzbari</v>
+      </c>
+      <c r="D380">
+        <v>2026</v>
+      </c>
+      <c r="E380">
+        <v>150000</v>
+      </c>
+      <c r="F380" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="G380" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>40</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Najwa</v>
+      </c>
+      <c r="C381" t="str">
+        <v>Najjar</v>
+      </c>
+      <c r="D381">
+        <v>2026</v>
+      </c>
+      <c r="E381">
+        <v>150000</v>
+      </c>
+      <c r="F381" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="G381" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>41</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Khadija</v>
+      </c>
+      <c r="C382" t="str">
+        <v>Tabbara</v>
+      </c>
+      <c r="D382">
+        <v>2026</v>
+      </c>
+      <c r="E382">
+        <v>150000</v>
+      </c>
+      <c r="F382" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="G382" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>42</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Fadi</v>
+      </c>
+      <c r="C383" t="str">
+        <v>Al-Halabi</v>
+      </c>
+      <c r="D383">
+        <v>2026</v>
+      </c>
+      <c r="E383">
+        <v>150000</v>
+      </c>
+      <c r="F383" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="G383" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>43</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Ahmad</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D384">
+        <v>2026</v>
+      </c>
+      <c r="E384">
+        <v>150000</v>
+      </c>
+      <c r="F384" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="G384" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>44</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Rana</v>
+      </c>
+      <c r="C385" t="str">
+        <v>Younis</v>
+      </c>
+      <c r="D385">
+        <v>2026</v>
+      </c>
+      <c r="E385">
+        <v>150000</v>
+      </c>
+      <c r="F385" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="G385" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>45</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Wassim</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D386">
+        <v>2026</v>
+      </c>
+      <c r="E386">
+        <v>150000</v>
+      </c>
+      <c r="F386" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="G386" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>46</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Mahmoud</v>
+      </c>
+      <c r="C387" t="str">
+        <v>Haddad</v>
+      </c>
+      <c r="D387">
+        <v>2026</v>
+      </c>
+      <c r="E387">
+        <v>150000</v>
+      </c>
+      <c r="F387" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="G387" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>47</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Ramez</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Al-Homsi</v>
+      </c>
+      <c r="D388">
+        <v>2026</v>
+      </c>
+      <c r="E388">
+        <v>150000</v>
+      </c>
+      <c r="F388" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="G388" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>48</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Bassam</v>
+      </c>
+      <c r="C389" t="str">
+        <v>Abdo</v>
+      </c>
+      <c r="D389">
+        <v>2026</v>
+      </c>
+      <c r="E389">
+        <v>150000</v>
+      </c>
+      <c r="F389" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="G389" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>49</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Ayman</v>
+      </c>
+      <c r="C390" t="str">
+        <v>Aboud</v>
+      </c>
+      <c r="D390">
+        <v>2026</v>
+      </c>
+      <c r="E390">
+        <v>150000</v>
+      </c>
+      <c r="F390" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="G390" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>50</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Tamer</v>
+      </c>
+      <c r="C391" t="str">
+        <v>Antaki</v>
+      </c>
+      <c r="D391">
+        <v>2026</v>
+      </c>
+      <c r="E391">
+        <v>150000</v>
+      </c>
+      <c r="F391" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="G391" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <v>51</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Omar</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Yacoub</v>
+      </c>
+      <c r="D392">
+        <v>2026</v>
+      </c>
+      <c r="E392">
+        <v>150000</v>
+      </c>
+      <c r="F392" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="G392" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <v>52</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Samir</v>
+      </c>
+      <c r="C393" t="str">
+        <v>Antaki</v>
+      </c>
+      <c r="D393">
+        <v>2026</v>
+      </c>
+      <c r="E393">
+        <v>150000</v>
+      </c>
+      <c r="F393" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="G393" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <v>53</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Hassan</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Al-Halabi</v>
+      </c>
+      <c r="D394">
+        <v>2026</v>
+      </c>
+      <c r="E394">
+        <v>150000</v>
+      </c>
+      <c r="F394" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="G394" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395">
+        <v>54</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Ramez</v>
+      </c>
+      <c r="C395" t="str">
+        <v>Al-Idlibi</v>
+      </c>
+      <c r="D395">
+        <v>2026</v>
+      </c>
+      <c r="E395">
+        <v>150000</v>
+      </c>
+      <c r="F395" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="G395" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396">
+        <v>55</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Hussein</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Naser</v>
+      </c>
+      <c r="D396">
+        <v>2026</v>
+      </c>
+      <c r="E396">
+        <v>150000</v>
+      </c>
+      <c r="F396" t="str">
+        <v>2026-02-24</v>
+      </c>
+      <c r="G396" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397">
+        <v>56</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Faisal</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Al-Kurdi</v>
+      </c>
+      <c r="D397">
+        <v>2026</v>
+      </c>
+      <c r="E397">
+        <v>150000</v>
+      </c>
+      <c r="F397" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="G397" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398">
+        <v>57</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Hanan</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Sabbagh</v>
+      </c>
+      <c r="D398">
+        <v>2026</v>
+      </c>
+      <c r="E398">
+        <v>150000</v>
+      </c>
+      <c r="F398" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="G398" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399">
+        <v>58</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Mahmoud</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Sabbagh</v>
+      </c>
+      <c r="D399">
+        <v>2026</v>
+      </c>
+      <c r="E399">
+        <v>150000</v>
+      </c>
+      <c r="F399" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="G399" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400">
+        <v>59</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Mahmoud</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D400">
+        <v>2026</v>
+      </c>
+      <c r="E400">
+        <v>150000</v>
+      </c>
+      <c r="F400" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="G400" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401">
+        <v>60</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Khadija</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Al-Shami</v>
+      </c>
+      <c r="D401">
+        <v>2026</v>
+      </c>
+      <c r="E401">
+        <v>150000</v>
+      </c>
+      <c r="F401" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="G401" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402">
+        <v>61</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Walid</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Daouk</v>
+      </c>
+      <c r="D402">
+        <v>2026</v>
+      </c>
+      <c r="E402">
+        <v>150000</v>
+      </c>
+      <c r="F402" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="G402" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403">
+        <v>62</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Kamal</v>
+      </c>
+      <c r="C403" t="str">
+        <v>Mardam-Bey</v>
+      </c>
+      <c r="D403">
+        <v>2026</v>
+      </c>
+      <c r="E403">
+        <v>150000</v>
+      </c>
+      <c r="F403" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="G403" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404">
+        <v>63</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Mohammad</v>
+      </c>
+      <c r="C404" t="str">
+        <v>Bani-Marjeh</v>
+      </c>
+      <c r="D404">
+        <v>2026</v>
+      </c>
+      <c r="E404">
+        <v>150000</v>
+      </c>
+      <c r="F404" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="G404" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405">
+        <v>64</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Talal</v>
+      </c>
+      <c r="C405" t="str">
+        <v>Othman</v>
+      </c>
+      <c r="D405">
+        <v>2026</v>
+      </c>
+      <c r="E405">
+        <v>150000</v>
+      </c>
+      <c r="F405" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="G405" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406">
+        <v>65</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Mohammad</v>
+      </c>
+      <c r="C406" t="str">
+        <v>Othman</v>
+      </c>
+      <c r="D406">
+        <v>2026</v>
+      </c>
+      <c r="E406">
+        <v>150000</v>
+      </c>
+      <c r="F406" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="G406" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407">
+        <v>66</v>
+      </c>
+      <c r="B407" t="str">
+        <v>Bassam</v>
+      </c>
+      <c r="C407" t="str">
+        <v>Hafez</v>
+      </c>
+      <c r="D407">
+        <v>2026</v>
+      </c>
+      <c r="E407">
+        <v>150000</v>
+      </c>
+      <c r="F407" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="G407" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408">
+        <v>67</v>
+      </c>
+      <c r="B408" t="str">
+        <v>Walid</v>
+      </c>
+      <c r="C408" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D408">
+        <v>2026</v>
+      </c>
+      <c r="E408">
+        <v>150000</v>
+      </c>
+      <c r="F408" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="G408" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409">
+        <v>68</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Iyad</v>
+      </c>
+      <c r="C409" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="D409">
+        <v>2026</v>
+      </c>
+      <c r="E409">
+        <v>150000</v>
+      </c>
+      <c r="F409" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="G409" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410">
+        <v>69</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Tamer</v>
+      </c>
+      <c r="C410" t="str">
+        <v>Wakim</v>
+      </c>
+      <c r="D410">
+        <v>2026</v>
+      </c>
+      <c r="E410">
+        <v>150000</v>
+      </c>
+      <c r="F410" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="G410" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411">
+        <v>70</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Kamal</v>
+      </c>
+      <c r="C411" t="str">
+        <v>Hafez</v>
+      </c>
+      <c r="D411">
+        <v>2026</v>
+      </c>
+      <c r="E411">
+        <v>150000</v>
+      </c>
+      <c r="F411" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="G411" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412">
+        <v>71</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Reem</v>
+      </c>
+      <c r="C412" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D412">
+        <v>2026</v>
+      </c>
+      <c r="E412">
+        <v>150000</v>
+      </c>
+      <c r="F412" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="G412" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413">
+        <v>72</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="C413" t="str">
+        <v>Al-Hassan</v>
+      </c>
+      <c r="D413">
+        <v>2026</v>
+      </c>
+      <c r="E413">
+        <v>150000</v>
+      </c>
+      <c r="F413" t="str">
+        <v>2026-01-31</v>
+      </c>
+      <c r="G413" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414">
+        <v>73</v>
+      </c>
+      <c r="B414" t="str">
+        <v>Saif</v>
+      </c>
+      <c r="C414" t="str">
+        <v>Tabbara</v>
+      </c>
+      <c r="D414">
+        <v>2026</v>
+      </c>
+      <c r="E414">
+        <v>150000</v>
+      </c>
+      <c r="F414" t="str">
+        <v>2026-02-05</v>
+      </c>
+      <c r="G414" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415">
+        <v>74</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Kamal</v>
+      </c>
+      <c r="C415" t="str">
+        <v>Haddad</v>
+      </c>
+      <c r="D415">
+        <v>2026</v>
+      </c>
+      <c r="E415">
+        <v>150000</v>
+      </c>
+      <c r="F415" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="G415" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416">
+        <v>75</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Ziad</v>
+      </c>
+      <c r="C416" t="str">
+        <v>Al-Shami</v>
+      </c>
+      <c r="D416">
+        <v>2026</v>
+      </c>
+      <c r="E416">
+        <v>150000</v>
+      </c>
+      <c r="F416" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G416" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417">
+        <v>76</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Yara</v>
+      </c>
+      <c r="C417" t="str">
+        <v>Younis</v>
+      </c>
+      <c r="D417">
+        <v>2026</v>
+      </c>
+      <c r="E417">
+        <v>150000</v>
+      </c>
+      <c r="F417" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="G417" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418">
+        <v>77</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Fares</v>
+      </c>
+      <c r="C418" t="str">
+        <v>Najjar</v>
+      </c>
+      <c r="D418">
+        <v>2026</v>
+      </c>
+      <c r="E418">
+        <v>150000</v>
+      </c>
+      <c r="F418" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="G418" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419">
+        <v>78</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Maha</v>
+      </c>
+      <c r="C419" t="str">
+        <v>Al-Halabi</v>
+      </c>
+      <c r="D419">
+        <v>2026</v>
+      </c>
+      <c r="E419">
+        <v>150000</v>
+      </c>
+      <c r="F419" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="G419" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420">
+        <v>79</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Anas</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D420">
+        <v>2026</v>
+      </c>
+      <c r="E420">
+        <v>150000</v>
+      </c>
+      <c r="F420" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="G420" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421">
+        <v>80</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Bilal</v>
+      </c>
+      <c r="C421" t="str">
+        <v>Al-Tartousi</v>
+      </c>
+      <c r="D421">
+        <v>2026</v>
+      </c>
+      <c r="E421">
+        <v>150000</v>
+      </c>
+      <c r="F421" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="G421" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422">
+        <v>81</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Saeed</v>
+      </c>
+      <c r="C422" t="str">
+        <v>Aboud</v>
+      </c>
+      <c r="D422">
+        <v>2026</v>
+      </c>
+      <c r="E422">
+        <v>150000</v>
+      </c>
+      <c r="F422" t="str">
+        <v>2026-01-18</v>
+      </c>
+      <c r="G422" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423">
+        <v>82</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Rana</v>
+      </c>
+      <c r="C423" t="str">
+        <v>Issa</v>
+      </c>
+      <c r="D423">
+        <v>2026</v>
+      </c>
+      <c r="E423">
+        <v>150000</v>
+      </c>
+      <c r="F423" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="G423" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424">
+        <v>83</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Karim</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Abdo</v>
+      </c>
+      <c r="D424">
+        <v>2026</v>
+      </c>
+      <c r="E424">
+        <v>150000</v>
+      </c>
+      <c r="F424" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="G424" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425">
+        <v>84</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Fadi</v>
+      </c>
+      <c r="C425" t="str">
+        <v>Aboud</v>
+      </c>
+      <c r="D425">
+        <v>2026</v>
+      </c>
+      <c r="E425">
+        <v>150000</v>
+      </c>
+      <c r="F425" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="G425" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426">
+        <v>85</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Ahmad</v>
+      </c>
+      <c r="C426" t="str">
+        <v>Yacoub</v>
+      </c>
+      <c r="D426">
+        <v>2026</v>
+      </c>
+      <c r="E426">
+        <v>150000</v>
+      </c>
+      <c r="F426" t="str">
+        <v>2026-02-01</v>
+      </c>
+      <c r="G426" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427">
+        <v>86</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Rami</v>
+      </c>
+      <c r="C427" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D427">
+        <v>2026</v>
+      </c>
+      <c r="E427">
+        <v>150000</v>
+      </c>
+      <c r="F427" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="G427" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428">
+        <v>87</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Bassam</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Al-Kuzbari</v>
+      </c>
+      <c r="D428">
+        <v>2026</v>
+      </c>
+      <c r="E428">
+        <v>150000</v>
+      </c>
+      <c r="F428" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="G428" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429">
+        <v>88</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Ranim</v>
+      </c>
+      <c r="C429" t="str">
+        <v>Al-Kuzbari</v>
+      </c>
+      <c r="D429">
+        <v>2026</v>
+      </c>
+      <c r="E429">
+        <v>150000</v>
+      </c>
+      <c r="F429" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="G429" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430">
+        <v>89</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Ranim</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Wakim</v>
+      </c>
+      <c r="D430">
+        <v>2026</v>
+      </c>
+      <c r="E430">
+        <v>150000</v>
+      </c>
+      <c r="F430" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="G430" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431">
+        <v>90</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Ayman</v>
+      </c>
+      <c r="C431" t="str">
+        <v>Habib</v>
+      </c>
+      <c r="D431">
+        <v>2026</v>
+      </c>
+      <c r="E431">
+        <v>150000</v>
+      </c>
+      <c r="F431" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G431" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432">
+        <v>91</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Dalia</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Al-Khatib</v>
+      </c>
+      <c r="D432">
+        <v>2026</v>
+      </c>
+      <c r="E432">
+        <v>150000</v>
+      </c>
+      <c r="F432" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="G432" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433">
+        <v>92</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Souad</v>
+      </c>
+      <c r="C433" t="str">
+        <v>Al-Tartousi</v>
+      </c>
+      <c r="D433">
+        <v>2026</v>
+      </c>
+      <c r="E433">
+        <v>150000</v>
+      </c>
+      <c r="F433" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="G433" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434">
+        <v>93</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Ziad</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Chalabi</v>
+      </c>
+      <c r="D434">
+        <v>2026</v>
+      </c>
+      <c r="E434">
+        <v>150000</v>
+      </c>
+      <c r="F434" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G434" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435">
+        <v>94</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Hassan</v>
+      </c>
+      <c r="C435" t="str">
+        <v>Atassi</v>
+      </c>
+      <c r="D435">
+        <v>2026</v>
+      </c>
+      <c r="E435">
+        <v>150000</v>
+      </c>
+      <c r="F435" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="G435" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436">
+        <v>95</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Layla</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D436">
+        <v>2026</v>
+      </c>
+      <c r="E436">
+        <v>150000</v>
+      </c>
+      <c r="F436" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="G436" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437">
+        <v>96</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Rana</v>
+      </c>
+      <c r="C437" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D437">
+        <v>2026</v>
+      </c>
+      <c r="E437">
+        <v>150000</v>
+      </c>
+      <c r="F437" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="G437" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438">
+        <v>97</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Rami</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Mansour</v>
+      </c>
+      <c r="D438">
+        <v>2026</v>
+      </c>
+      <c r="E438">
+        <v>150000</v>
+      </c>
+      <c r="F438" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="G438" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439">
+        <v>98</v>
+      </c>
+      <c r="B439" t="str">
+        <v>Talal</v>
+      </c>
+      <c r="C439" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D439">
+        <v>2026</v>
+      </c>
+      <c r="E439">
+        <v>150000</v>
+      </c>
+      <c r="F439" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G439" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440">
+        <v>99</v>
+      </c>
+      <c r="B440" t="str">
+        <v>Reem</v>
+      </c>
+      <c r="C440" t="str">
+        <v>Antaki</v>
+      </c>
+      <c r="D440">
+        <v>2026</v>
+      </c>
+      <c r="E440">
+        <v>150000</v>
+      </c>
+      <c r="F440" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G440" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441">
+        <v>100</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Hassan</v>
+      </c>
+      <c r="C441" t="str">
+        <v>Mardini</v>
+      </c>
+      <c r="D441">
+        <v>2026</v>
+      </c>
+      <c r="E441">
+        <v>150000</v>
+      </c>
+      <c r="F441" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="G441" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442">
+        <v>101</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Majd</v>
+      </c>
+      <c r="C442" t="str">
+        <v>Bani-Marjeh</v>
+      </c>
+      <c r="D442">
+        <v>2026</v>
+      </c>
+      <c r="E442">
+        <v>150000</v>
+      </c>
+      <c r="F442" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="G442" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443">
+        <v>102</v>
+      </c>
+      <c r="B443" t="str">
+        <v>Rabih</v>
+      </c>
+      <c r="C443" t="str">
+        <v>Al-Shami</v>
+      </c>
+      <c r="D443">
+        <v>2026</v>
+      </c>
+      <c r="E443">
+        <v>150000</v>
+      </c>
+      <c r="F443" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="G443" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444">
+        <v>103</v>
+      </c>
+      <c r="B444" t="str">
+        <v>Rami</v>
+      </c>
+      <c r="C444" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D444">
+        <v>2026</v>
+      </c>
+      <c r="E444">
+        <v>150000</v>
+      </c>
+      <c r="F444" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="G444" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445">
+        <v>104</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Dalia</v>
+      </c>
+      <c r="C445" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D445">
+        <v>2026</v>
+      </c>
+      <c r="E445">
+        <v>150000</v>
+      </c>
+      <c r="F445" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="G445" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446">
+        <v>105</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Ghassan</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Habib</v>
+      </c>
+      <c r="D446">
+        <v>2026</v>
+      </c>
+      <c r="E446">
+        <v>150000</v>
+      </c>
+      <c r="F446" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="G446" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447">
+        <v>106</v>
+      </c>
+      <c r="B447" t="str">
+        <v>Nader</v>
+      </c>
+      <c r="C447" t="str">
+        <v>Al-Homsi</v>
+      </c>
+      <c r="D447">
+        <v>2026</v>
+      </c>
+      <c r="E447">
+        <v>150000</v>
+      </c>
+      <c r="F447" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="G447" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448">
+        <v>107</v>
+      </c>
+      <c r="B448" t="str">
+        <v>Fares</v>
+      </c>
+      <c r="C448" t="str">
+        <v>Sabbagh</v>
+      </c>
+      <c r="D448">
+        <v>2026</v>
+      </c>
+      <c r="E448">
+        <v>150000</v>
+      </c>
+      <c r="F448" t="str">
+        <v>2026-04-07</v>
+      </c>
+      <c r="G448" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449">
+        <v>108</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Malek</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Othman</v>
+      </c>
+      <c r="D449">
+        <v>2026</v>
+      </c>
+      <c r="E449">
+        <v>150000</v>
+      </c>
+      <c r="F449" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G449" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450">
+        <v>109</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Wafa</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Sabbagh</v>
+      </c>
+      <c r="D450">
+        <v>2026</v>
+      </c>
+      <c r="E450">
+        <v>150000</v>
+      </c>
+      <c r="F450" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="G450" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451">
+        <v>110</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Ayman</v>
+      </c>
+      <c r="C451" t="str">
+        <v>Bakri</v>
+      </c>
+      <c r="D451">
+        <v>2026</v>
+      </c>
+      <c r="E451">
+        <v>150000</v>
+      </c>
+      <c r="F451" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="G451" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452">
+        <v>111</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Samir</v>
+      </c>
+      <c r="C452" t="str">
+        <v>Khoury</v>
+      </c>
+      <c r="D452">
+        <v>2026</v>
+      </c>
+      <c r="E452">
+        <v>150000</v>
+      </c>
+      <c r="F452" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="G452" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453">
+        <v>112</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Tarek</v>
+      </c>
+      <c r="C453" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="D453">
+        <v>2026</v>
+      </c>
+      <c r="E453">
+        <v>150000</v>
+      </c>
+      <c r="F453" t="str">
+        <v>2026-01-09</v>
+      </c>
+      <c r="G453" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454">
+        <v>113</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Nabil</v>
+      </c>
+      <c r="C454" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D454">
+        <v>2026</v>
+      </c>
+      <c r="E454">
+        <v>150000</v>
+      </c>
+      <c r="F454" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="G454" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455">
+        <v>114</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Iyad</v>
+      </c>
+      <c r="C455" t="str">
+        <v>Younis</v>
+      </c>
+      <c r="D455">
+        <v>2026</v>
+      </c>
+      <c r="E455">
+        <v>150000</v>
+      </c>
+      <c r="F455" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="G455" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456">
+        <v>115</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Najwa</v>
+      </c>
+      <c r="C456" t="str">
+        <v>Saadeh</v>
+      </c>
+      <c r="D456">
+        <v>2026</v>
+      </c>
+      <c r="E456">
+        <v>150000</v>
+      </c>
+      <c r="F456" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="G456" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457">
+        <v>116</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Adnan</v>
+      </c>
+      <c r="C457" t="str">
+        <v>Haddad</v>
+      </c>
+      <c r="D457">
+        <v>2026</v>
+      </c>
+      <c r="E457">
+        <v>150000</v>
+      </c>
+      <c r="F457" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="G457" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458">
+        <v>117</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Imad</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Al-Homsi</v>
+      </c>
+      <c r="D458">
+        <v>2026</v>
+      </c>
+      <c r="E458">
+        <v>150000</v>
+      </c>
+      <c r="F458" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="G458" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459">
+        <v>118</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Usama</v>
+      </c>
+      <c r="C459" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D459">
+        <v>2026</v>
+      </c>
+      <c r="E459">
+        <v>150000</v>
+      </c>
+      <c r="F459" t="str">
+        <v>2026-02-28</v>
+      </c>
+      <c r="G459" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460">
+        <v>119</v>
+      </c>
+      <c r="B460" t="str">
+        <v>Ghassan</v>
+      </c>
+      <c r="C460" t="str">
+        <v>Al-Idlibi</v>
+      </c>
+      <c r="D460">
+        <v>2026</v>
+      </c>
+      <c r="E460">
+        <v>150000</v>
+      </c>
+      <c r="F460" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="G460" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461">
+        <v>120</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Adnan</v>
+      </c>
+      <c r="C461" t="str">
+        <v>Khoury</v>
+      </c>
+      <c r="D461">
+        <v>2026</v>
+      </c>
+      <c r="E461">
+        <v>150000</v>
+      </c>
+      <c r="F461" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="G461" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462">
+        <v>121</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Bashar</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Daouk</v>
+      </c>
+      <c r="D462">
+        <v>2026</v>
+      </c>
+      <c r="E462">
+        <v>150000</v>
+      </c>
+      <c r="F462" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="G462" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463">
+        <v>122</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Nader</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Antaki</v>
+      </c>
+      <c r="D463">
+        <v>2026</v>
+      </c>
+      <c r="E463">
+        <v>150000</v>
+      </c>
+      <c r="F463" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="G463" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464">
+        <v>123</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Ali</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Al-Kurdi</v>
+      </c>
+      <c r="D464">
+        <v>2026</v>
+      </c>
+      <c r="E464">
+        <v>150000</v>
+      </c>
+      <c r="F464" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G464" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465">
+        <v>124</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Jalal</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Aboud</v>
+      </c>
+      <c r="D465">
+        <v>2026</v>
+      </c>
+      <c r="E465">
+        <v>150000</v>
+      </c>
+      <c r="F465" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="G465" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466">
+        <v>125</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Wassim</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Sleiman</v>
+      </c>
+      <c r="D466">
+        <v>2026</v>
+      </c>
+      <c r="E466">
+        <v>150000</v>
+      </c>
+      <c r="F466" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="G466" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467">
+        <v>126</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Khaled</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Saleh</v>
+      </c>
+      <c r="D467">
+        <v>2026</v>
+      </c>
+      <c r="E467">
+        <v>150000</v>
+      </c>
+      <c r="F467" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="G467" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468">
+        <v>127</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Hisham</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Kanaan</v>
+      </c>
+      <c r="D468">
+        <v>2026</v>
+      </c>
+      <c r="E468">
+        <v>150000</v>
+      </c>
+      <c r="F468" t="str">
+        <v>2026-02-07</v>
+      </c>
+      <c r="G468" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469">
+        <v>128</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Lamia</v>
+      </c>
+      <c r="C469" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D469">
+        <v>2026</v>
+      </c>
+      <c r="E469">
+        <v>150000</v>
+      </c>
+      <c r="F469" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="G469" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470">
+        <v>129</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Khaled</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Al-Ahmad</v>
+      </c>
+      <c r="D470">
+        <v>2026</v>
+      </c>
+      <c r="E470">
+        <v>150000</v>
+      </c>
+      <c r="F470" t="str">
+        <v>2026-02-04</v>
+      </c>
+      <c r="G470" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471">
+        <v>130</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Tamer</v>
+      </c>
+      <c r="C471" t="str">
+        <v>Bani-Marjeh</v>
+      </c>
+      <c r="D471">
+        <v>2026</v>
+      </c>
+      <c r="E471">
+        <v>150000</v>
+      </c>
+      <c r="F471" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="G471" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472">
+        <v>131</v>
+      </c>
+      <c r="B472" t="str">
+        <v>Omar</v>
+      </c>
+      <c r="C472" t="str">
+        <v>Al-Halabi</v>
+      </c>
+      <c r="D472">
+        <v>2026</v>
+      </c>
+      <c r="E472">
+        <v>150000</v>
+      </c>
+      <c r="F472" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G472" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473">
+        <v>132</v>
+      </c>
+      <c r="B473" t="str">
+        <v>Jihad</v>
+      </c>
+      <c r="C473" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D473">
+        <v>2026</v>
+      </c>
+      <c r="E473">
+        <v>150000</v>
+      </c>
+      <c r="F473" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="G473" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474">
+        <v>133</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Sami</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Wakim</v>
+      </c>
+      <c r="D474">
+        <v>2026</v>
+      </c>
+      <c r="E474">
+        <v>150000</v>
+      </c>
+      <c r="F474" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="G474" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475">
+        <v>134</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Majd</v>
+      </c>
+      <c r="C475" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D475">
+        <v>2026</v>
+      </c>
+      <c r="E475">
+        <v>150000</v>
+      </c>
+      <c r="F475" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="G475" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476">
+        <v>135</v>
+      </c>
+      <c r="B476" t="str">
+        <v>Ghassan</v>
+      </c>
+      <c r="C476" t="str">
+        <v>Al-Rifai</v>
+      </c>
+      <c r="D476">
+        <v>2026</v>
+      </c>
+      <c r="E476">
+        <v>150000</v>
+      </c>
+      <c r="F476" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="G476" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477">
+        <v>136</v>
+      </c>
+      <c r="B477" t="str">
+        <v>Adnan</v>
+      </c>
+      <c r="C477" t="str">
+        <v>Tlass</v>
+      </c>
+      <c r="D477">
+        <v>2026</v>
+      </c>
+      <c r="E477">
+        <v>150000</v>
+      </c>
+      <c r="F477" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="G477" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478">
+        <v>137</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Ranim</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Saadeh</v>
+      </c>
+      <c r="D478">
+        <v>2026</v>
+      </c>
+      <c r="E478">
+        <v>150000</v>
+      </c>
+      <c r="F478" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="G478" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479">
+        <v>138</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Samir</v>
+      </c>
+      <c r="C479" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D479">
+        <v>2026</v>
+      </c>
+      <c r="E479">
+        <v>150000</v>
+      </c>
+      <c r="F479" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="G479" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480">
+        <v>139</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Ahmad</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Saab</v>
+      </c>
+      <c r="D480">
+        <v>2026</v>
+      </c>
+      <c r="E480">
+        <v>150000</v>
+      </c>
+      <c r="F480" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="G480" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481">
+        <v>140</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Reem</v>
+      </c>
+      <c r="C481" t="str">
+        <v>Wakim</v>
+      </c>
+      <c r="D481">
+        <v>2026</v>
+      </c>
+      <c r="E481">
+        <v>150000</v>
+      </c>
+      <c r="F481" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="G481" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482">
+        <v>141</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Jihad</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Daouk</v>
+      </c>
+      <c r="D482">
+        <v>2026</v>
+      </c>
+      <c r="E482">
+        <v>150000</v>
+      </c>
+      <c r="F482" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="G482" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483">
+        <v>142</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Bashar</v>
+      </c>
+      <c r="C483" t="str">
+        <v>Al-Homsi</v>
+      </c>
+      <c r="D483">
+        <v>2026</v>
+      </c>
+      <c r="E483">
+        <v>150000</v>
+      </c>
+      <c r="F483" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="G483" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <v>143</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Mohammad</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Mansour</v>
+      </c>
+      <c r="D484">
+        <v>2026</v>
+      </c>
+      <c r="E484">
+        <v>150000</v>
+      </c>
+      <c r="F484" t="str">
+        <v>2026-03-07</v>
+      </c>
+      <c r="G484" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>144</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Faisal</v>
+      </c>
+      <c r="C485" t="str">
+        <v>Al-Hassan</v>
+      </c>
+      <c r="D485">
+        <v>2026</v>
+      </c>
+      <c r="E485">
+        <v>150000</v>
+      </c>
+      <c r="F485" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="G485" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486">
+        <v>145</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Yousef</v>
+      </c>
+      <c r="C486" t="str">
+        <v>Saab</v>
+      </c>
+      <c r="D486">
+        <v>2026</v>
+      </c>
+      <c r="E486">
+        <v>150000</v>
+      </c>
+      <c r="F486" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="G486" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487">
+        <v>146</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Hassan</v>
+      </c>
+      <c r="C487" t="str">
+        <v>Khalil</v>
+      </c>
+      <c r="D487">
+        <v>2026</v>
+      </c>
+      <c r="E487">
+        <v>150000</v>
+      </c>
+      <c r="F487" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="G487" t="str">
+        <v>Paid in cash at the office</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488">
+        <v>147</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Ziad</v>
+      </c>
+      <c r="C488" t="str">
+        <v>Saab</v>
+      </c>
+      <c r="D488">
+        <v>2026</v>
+      </c>
+      <c r="E488">
+        <v>150000</v>
+      </c>
+      <c r="F488" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="G488" t="str">
+        <v>Paid online</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489">
+        <v>148</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Hassan</v>
+      </c>
+      <c r="C489" t="str">
+        <v>Othman</v>
+      </c>
+      <c r="D489">
+        <v>2026</v>
+      </c>
+      <c r="E489">
+        <v>150000</v>
+      </c>
+      <c r="F489" t="str">
+        <v>2026-03-21</v>
+      </c>
+      <c r="G489" t="str">
+        <v>Paid by credit card</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490">
+        <v>149</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Wassim</v>
+      </c>
+      <c r="C490" t="str">
+        <v>Khoja</v>
+      </c>
+      <c r="D490">
+        <v>2026</v>
+      </c>
+      <c r="E490">
+        <v>150000</v>
+      </c>
+      <c r="F490" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="G490" t="str">
+        <v>Paid via mobile wallet</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491">
+        <v>150</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Bashar</v>
+      </c>
+      <c r="C491" t="str">
+        <v>Al-Rifai</v>
+      </c>
+      <c r="D491">
+        <v>2026</v>
+      </c>
+      <c r="E491">
+        <v>150000</v>
+      </c>
+      <c r="F491" t="str">
+        <v>2026-01-31</v>
+      </c>
+      <c r="G491" t="str">
+        <v>Paid via bank transfer</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G341"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G491"/>
   </ignoredErrors>
 </worksheet>
 </file>